--- a/data/fred_api_data.xlsx
+++ b/data/fred_api_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.06551709188650201</v>
+        <v>0.06516665582843806</v>
       </c>
       <c r="C131" t="n">
         <v>0.07099810387236771</v>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.06264871411270212</v>
+        <v>0.06127733846263439</v>
       </c>
       <c r="C132" t="n">
         <v>0.1458158998599113</v>
@@ -2171,7 +2171,7 @@
         <v>0.03828039297789076</v>
       </c>
       <c r="C134" t="n">
-        <v>0.1024997314830034</v>
+        <v>0.1025346710440331</v>
       </c>
     </row>
     <row r="135">
@@ -2181,10 +2181,23 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0382052873025398</v>
+        <v>0.04082608636665808</v>
       </c>
       <c r="C135" t="n">
-        <v>0.07094126005029389</v>
+        <v>0.07306001295559161</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0.05030681069019738</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.0009964570416296503</v>
       </c>
     </row>
   </sheetData>
